--- a/資金費率計算.xlsx
+++ b/資金費率計算.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cheng-kaihuang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cheng-kaihuang/HL-Delta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CA6059-37C3-A140-8C87-0AAB14820A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E77FBBB-02FB-134D-BA3D-C548CD0DA9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16820" xr2:uid="{81ECAD68-8E7D-5449-8203-1414CDC5E683}"/>
+    <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16820" activeTab="1" xr2:uid="{81ECAD68-8E7D-5449-8203-1414CDC5E683}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="資金費率" sheetId="1" r:id="rId1"/>
+    <sheet name="下單價格差距計算" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
   <si>
     <t>交易費用</t>
   </si>
@@ -107,13 +108,88 @@
   </si>
   <si>
     <t>年化 ($)</t>
+  </si>
+  <si>
+    <t>種類</t>
+  </si>
+  <si>
+    <t>買/賣</t>
+  </si>
+  <si>
+    <t>buy</t>
+  </si>
+  <si>
+    <t>console顯示 (Bot下單)</t>
+  </si>
+  <si>
+    <t>成交數量</t>
+  </si>
+  <si>
+    <t>成交價格</t>
+  </si>
+  <si>
+    <t>訂單編號</t>
+  </si>
+  <si>
+    <t>動作</t>
+  </si>
+  <si>
+    <t>開倉</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>181186190676</t>
+  </si>
+  <si>
+    <t>181186051836</t>
+  </si>
+  <si>
+    <t>Hyperliquid前端顯示</t>
+  </si>
+  <si>
+    <t>平倉</t>
+  </si>
+  <si>
+    <t>open short</t>
+  </si>
+  <si>
+    <t>close short</t>
+  </si>
+  <si>
+    <t>181189806185</t>
+  </si>
+  <si>
+    <t>181189557657</t>
+  </si>
+  <si>
+    <t>181193823848</t>
+  </si>
+  <si>
+    <t>181193929722</t>
+  </si>
+  <si>
+    <t>181195900508</t>
+  </si>
+  <si>
+    <t>Hyperliquid真正成交</t>
+  </si>
+  <si>
+    <t>181196099625</t>
+  </si>
+  <si>
+    <t>盈虧 (不計手續費)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -124,6 +200,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -149,7 +232,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -157,11 +240,128 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -179,6 +379,62 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -788,4 +1044,438 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E243DD73-3715-EF47-84AC-688E69564FF5}">
+  <dimension ref="C2:L22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" style="7"/>
+    <col min="3" max="3" width="20" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="7" customWidth="1"/>
+    <col min="5" max="8" width="10.83203125" style="7"/>
+    <col min="9" max="9" width="17" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="H4" s="24">
+        <v>45.387</v>
+      </c>
+      <c r="I4" s="24"/>
+      <c r="J4" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C5" s="12"/>
+      <c r="D5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H5" s="13">
+        <v>45.271999999999998</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H6" s="25">
+        <v>45.28</v>
+      </c>
+      <c r="I6" s="25">
+        <f>H6-H10</f>
+        <v>-0.15099999999999625</v>
+      </c>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="17"/>
+      <c r="D7" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="H7" s="18">
+        <v>45.348999999999997</v>
+      </c>
+      <c r="I7" s="18">
+        <f>H7-H11</f>
+        <v>-0.15000000000000568</v>
+      </c>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="H8" s="24">
+        <v>45.014000000000003</v>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C9" s="12"/>
+      <c r="D9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H9" s="14">
+        <v>45.94</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H10" s="26">
+        <v>45.430999999999997</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="17"/>
+      <c r="D11" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="H11" s="18">
+        <v>45.499000000000002</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="13" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="21"/>
+      <c r="D14" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="H15" s="24">
+        <v>45.436999999999998</v>
+      </c>
+      <c r="I15" s="24"/>
+      <c r="J15" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C16" s="12"/>
+      <c r="D16" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H16" s="13">
+        <v>45.317999999999998</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H17" s="25">
+        <v>45.332000000000001</v>
+      </c>
+      <c r="I17" s="25">
+        <f>H17-H21</f>
+        <v>0.20100000000000051</v>
+      </c>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="3:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="17"/>
+      <c r="D18" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="H18" s="18">
+        <v>45.390999999999998</v>
+      </c>
+      <c r="I18" s="18">
+        <f>H18-H22</f>
+        <v>0.22299999999999898</v>
+      </c>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="H19" s="24">
+        <v>44.710999999999999</v>
+      </c>
+      <c r="I19" s="24"/>
+      <c r="J19" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C20" s="12"/>
+      <c r="D20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H20" s="14">
+        <v>45.615000000000002</v>
+      </c>
+      <c r="I20" s="14"/>
+      <c r="J20" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C21" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H21" s="26">
+        <v>45.131</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="16"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="3:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="17"/>
+      <c r="D22" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="H22" s="18">
+        <v>45.167999999999999</v>
+      </c>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>